--- a/Teoría de la información/Árboles.xlsx
+++ b/Teoría de la información/Árboles.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Teoría de la información\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ran\Programas\GitHub\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F57C337A-70DB-4F6A-ABEA-BEA5D144FCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{11A3EADE-C24F-4ABF-B542-FA9BF0BEB25D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,7 +478,7 @@
         <xdr:cNvPr id="2" name="Rectángulo 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139439FC-DED7-FF91-A0A7-39673CE90EB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{139439FC-DED7-FF91-A0A7-39673CE90EB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -557,7 +557,7 @@
         <xdr:cNvPr id="3" name="Rectángulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{721A367F-8E73-A319-3916-CCAEC078BE47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{721A367F-8E73-A319-3916-CCAEC078BE47}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -620,14 +620,14 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>2230</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Entrada de lápiz 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FCF3ACF-104B-A762-72A3-8AA44EB22FC1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7FCF3ACF-104B-A762-72A3-8AA44EB22FC1}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -640,7 +640,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Entrada de lápiz 3">
@@ -685,14 +685,14 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Entrada de lápiz 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0B0F75-51B2-2D44-6472-0D1D420ABEBC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E0B0F75-51B2-2D44-6472-0D1D420ABEBC}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -705,7 +705,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Entrada de lápiz 6">
@@ -750,14 +750,14 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>55080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Entrada de lápiz 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B94A17-3A72-21BA-901D-37ED9716B0D1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C1B94A17-3A72-21BA-901D-37ED9716B0D1}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -770,7 +770,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Entrada de lápiz 7">
@@ -815,14 +815,14 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="11" name="Entrada de lápiz 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F35F2452-1F9A-59B8-465B-D6D4E4DC01D9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F35F2452-1F9A-59B8-465B-D6D4E4DC01D9}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -835,7 +835,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="11" name="Entrada de lápiz 10">
@@ -880,14 +880,14 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>104400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Entrada de lápiz 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D78BB5CE-C72C-8865-36B5-2F798DBB6F3D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D78BB5CE-C72C-8865-36B5-2F798DBB6F3D}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -900,7 +900,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Entrada de lápiz 17">
@@ -945,14 +945,14 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>79560</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="25" name="Entrada de lápiz 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC60CE2-B5CA-2DAD-CED7-437877C0A9FA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FFC60CE2-B5CA-2DAD-CED7-437877C0A9FA}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -965,7 +965,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="25" name="Entrada de lápiz 24">
@@ -1010,14 +1010,14 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="Entrada de lápiz 27">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B55704-EE9E-F9E3-C5B6-C6CF5A771209}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5B55704-EE9E-F9E3-C5B6-C6CF5A771209}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1030,7 +1030,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="Entrada de lápiz 27">
@@ -1080,7 +1080,7 @@
         <xdr:cNvPr id="29" name="Rectángulo 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5A1BEF7-DADC-490C-404E-546D8F6C5C2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B5A1BEF7-DADC-490C-404E-546D8F6C5C2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1148,7 +1148,7 @@
         <xdr:cNvPr id="30" name="Rectángulo 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6616C2D6-5BAA-C4AC-C4A9-4524E177B7E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6616C2D6-5BAA-C4AC-C4A9-4524E177B7E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1240,7 +1240,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2893 0 24575,'-15'16'0,"0"0"0,-17 28 0,5-8 0,-229 305 0,21 19 0,44-14 0,-227 358 0,290-533 0,-202 205 0,-184 207 0,107-116 0,386-443-83,-139 160 297,130-147-588,3 2 0,1 1 0,-21 45 0,34-57-6452</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3070 0 24575,'-16'15'0,"0"1"0,-18 25 0,5-6 0,-242 290 0,21 18 0,48-13 0,-242 342 0,308-509 0,-214 196 0,-195 197 0,113-111 0,410-422-83,-148 153 297,138-141-588,3 2 0,2 1 0,-23 43 0,36-54-6452</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1267,7 +1267,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"1"0"0,0 0 0,-1 0 0,1 1 0,0-1 0,-1 2 0,6 2 0,7 2 0,181 74 0,201 115 0,-244-107 0,-4 7 0,191 157 0,241 272 0,-436-380 0,-7 7 0,131 184 0,183 255 0,-234-311 0,-196-248 0,-3-6 0,18 31 0,123 180 0,27 46 0,-149-211 0,66 86 0,-79-123 0,1-1 0,1-2 0,2-1 0,40 30 0,-33-29-1365,-25-18-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"2"0"0,0 0 0,-2 0 0,2 1 0,-1-1 0,-1 2 0,7 1 0,8 3 0,197 70 0,219 110 0,-266-102 0,-5 7 0,209 149 0,262 260 0,-474-363 0,-9 7 0,144 175 0,199 244 0,-256-297 0,-212-236 0,-4-7 0,19 31 0,135 171 0,29 44 0,-163-202 0,73 83 0,-86-118 0,0 0 0,2-3 0,2 0 0,43 28 0,-35-27-1365,-28-18-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1294,7 +1294,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"1"0"0,-1-1 0,1 2 0,-1-1 0,11 5 0,4 0 0,198 64 0,-186-57 0,0 1 0,-1 1 0,-1 2 0,46 33 0,-62-36 0,0 0 0,0 1 0,-2 0 0,0 1 0,13 21 0,-1 13 0,-22-43 0,0 0 0,1 0 0,0 0 0,1-1 0,0 1 0,0-1 0,0 0 0,0 0 0,1-1 0,7 7 0,319 220 0,-312-219 0,28 20 0,-1 3 0,67 69 0,-100-91 0,-1 1 0,15 24 0,-9-13 0,6 22-164,-18-34-1037,0-1-5625</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'6'1'0,"1"0"0,-2-1 0,2 2 0,-1-1 0,12 4 0,5 1 0,225 61 0,-212-55 0,1 2 0,-2 0 0,-1 2 0,52 32 0,-70-35 0,0 1 0,0 0 0,-2 0 0,-1 2 0,16 19 0,-2 13 0,-25-42 0,1 1 0,0 0 0,1-1 0,0 0 0,1 1 0,-1-2 0,1 1 0,-1 0 0,2-1 0,8 6 0,362 210 0,-354-208 0,31 18 0,0 4 0,75 65 0,-113-87 0,-1 1 0,16 24 0,-9-14 0,6 22-164,-20-32-1037,0-2-5625</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1321,8 +1321,8 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1585 0 24575,'-5'2'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1 0 0,-1 1 0,1-1 0,0 1 0,-5 5 0,-5 1 0,-46 33 0,2 3 0,1 3 0,-65 72 0,111-110 0,-25 25 0,2 2 0,2 1 0,-50 75 0,-94 214 0,152-285 0,4-6 0,-1-1 0,-33 41 0,6-14 0,3 2 0,-52 98 0,-52 147 0,63-132 0,70-147 0,-1 0 0,-1-2 0,-33 40 0,1-1 0,-97 138-1365,136-191-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1910.02">1522 127 24575,'0'-4'0,"0"-1"0,0 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,4-7 0,-5 11 0,1 1 0,-1-1 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,0-1 0,1 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,2 2 0,10 7 0,-1 2 0,-1-1 0,0 2 0,0-1 0,-1 2 0,13 19 0,-10-13 0,24 39 0,-2 2 0,-3 0 0,28 77 0,-38-84 0,-9-25 0,-1 1 0,-1 0 0,-2 1 0,-2 0 0,9 56 0,-16-76 0,1-1 0,1 0 0,-1 1 0,2-1 0,-1-1 0,1 1 0,8 12 0,43 63 0,-19-33 0,27 39 0,20 33 0,443 918-570,-433-856-700,-87-172-5081</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1683 0 24575,'-5'2'0,"1"-1"0,-2 0 0,2 1 0,-1 0 0,0 0 0,0 0 0,1 0 0,0 1 0,-6 5 0,-5 0 0,-49 33 0,3 1 0,0 4 0,-68 69 0,117-106 0,-26 25 0,2 1 0,2 1 0,-53 72 0,-100 205 0,161-273 0,5-6 0,-1-1 0,-36 40 0,8-14 0,2 2 0,-55 94 0,-55 140 0,66-126 0,75-140 0,-1-1 0,-1-1 0,-35 38 0,1-1 0,-103 132-1365,144-183-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1910.02">1616 121 24575,'0'-4'0,"0"0"0,0-1 0,1 1 0,-1-1 0,1 1 0,0 0 0,0-1 0,5-7 0,-6 12 0,1 0 0,-1-1 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,1-1 0,0 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,1 1 0,-2-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,2 2 0,11 6 0,-1 3 0,-1-2 0,0 3 0,-1-2 0,0 2 0,13 19 0,-10-13 0,26 37 0,-3 3 0,-3-1 0,30 74 0,-41-81 0,-9-23 0,-1 0 0,-1 1 0,-3 1 0,-1-1 0,9 54 0,-17-72 0,1-2 0,1 1 0,-1 0 0,2 0 0,0-1 0,0 0 0,9 12 0,45 60 0,-20-31 0,29 37 0,21 31 0,471 877-570,-460-817-700,-93-165-5081</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1349,10 +1349,10 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1857 148 24575,'-5'1'0,"0"1"0,-1 0 0,1 0 0,0 0 0,0 0 0,0 1 0,0 0 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 1 0,-7 9 0,1-3 0,-288 296 0,130-127 0,43-48 0,98-101-1365,17-20-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2406.82">1941 0 24575,'12'9'0,"-1"0"0,1-2 0,1 1 0,-1-1 0,1-1 0,21 7 0,-12-4 0,152 55 0,-140-49 0,-1 1 0,-1 2 0,-1 1 0,47 38 0,-32-23 0,-35-27 0,0 0 0,0 1 0,-1 1 0,-1 0 0,0 0 0,0 0 0,10 15 0,-2-2 0,0-2 0,1 0 0,2-1 0,0-1 0,0-1 0,26 16 0,-11-9 0,-25-19 0,-1 0 0,-1 1 0,1 0 0,-1 1 0,0 0 0,0 0 0,-1 0 0,10 15 0,55 74 0,-15-23 0,92 131 0,-109-147-1365,-28-42-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6450.08">988 973 24575,'-1'7'0,"-1"-1"0,0 1 0,-1-1 0,1 0 0,-1 0 0,-1 0 0,1 0 0,-1-1 0,-4 6 0,-3 5 0,-40 57 0,-117 126 0,73-92 0,57-60 0,1 2 0,-59 106 0,-21 26 0,56-93 0,11-15 0,-3-2 0,-91 96 0,118-140-1365,18-18-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8599.32">945 931 24575,'1'4'0,"0"0"0,0 0 0,0-1 0,0 1 0,0-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 0 0,3 3 0,29 34 0,-33-39 0,50 49 0,3-2 0,114 79 0,-129-101 0,119 88 0,-132-92 0,-1 0 0,-1 2 0,38 47 0,-28-29 0,-20-26 0,-2 0 0,19 28 0,-9 9 0,-18-39 0,2-1 0,10 21 0,172 263 0,-41-74 0,121 239 0,-256-440-120,-5-6-58,1 0 0,1 0 0,0-1 1,1-1-1,1 0 0,20 21 0,-22-27-6648</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1960 141 24575,'-5'1'0,"0"1"0,-1 0 0,0 0 0,1 0 0,0 0 0,-1 0 0,1 1 0,1 0 0,-1 0 0,0 1 0,1-1 0,0 0 0,-8 10 0,2-4 0,-305 283 0,138-121 0,45-47 0,103-95-1365,19-19-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2406.82">2049 0 24575,'13'9'0,"-2"-1"0,2-1 0,1 0 0,-2 0 0,2-1 0,22 6 0,-13-3 0,161 52 0,-148-47 0,-1 1 0,-1 2 0,-2 2 0,51 35 0,-35-22 0,-36-25 0,-1 0 0,1 0 0,-1 2 0,-2-1 0,1 1 0,-1 0 0,11 13 0,-2-1 0,0-2 0,1 1 0,2-2 0,0-1 0,0-1 0,28 15 0,-12-8 0,-27-18 0,0 0 0,-2 1 0,2-1 0,-2 2 0,1 0 0,-1-1 0,0 1 0,10 14 0,58 70 0,-16-21 0,97 124 0,-115-139-1365,-29-41-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6450.08">1043 927 24575,'-1'7'0,"-1"-1"0,0 0 0,-1 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,-1-1 0,-5 5 0,-2 5 0,-43 55 0,-124 120 0,78-88 0,60-58 0,1 3 0,-62 101 0,-23 24 0,60-88 0,11-14 0,-3-3 0,-96 92 0,124-133-1365,20-17-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8599.32">998 887 24575,'1'4'0,"0"0"0,0 0 0,0-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,0-1 0,4 4 0,30 32 0,-35-37 0,53 47 0,3-2 0,120 75 0,-136-97 0,126 85 0,-140-88 0,0 0 0,-2 2 0,41 44 0,-31-27 0,-20-24 0,-2-1 0,20 27 0,-10 8 0,-19-36 0,2-2 0,11 21 0,182 250 0,-44-71 0,128 228 0,-270-419-120,-6-5-58,1-1 0,2 0 0,-1-1 1,2 0-1,1-1 0,20 20 0,-22-25-6648</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1380,10 +1380,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 16 24575,'971'-11'-38,"-644"6"-497,647 40 420,-865-25 125,237 30-31,-248-25 84,145 43 0,-48 7 224,194 92-1,387 158-286,-452-192 0,-157-55 0,152 54 0,-245-96-35,-51-16-187,0-2 0,0 0 1,1-2-1,0 0 1,32 2-1,-35-7-6604</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2558.85">5639 828 24575,'8'3'0,"12"13"0,21 10 0,15 11 0,15 14 0,11 8 0,1 5 0,1 3 0,-6-7 0,-2 0 0,-7-6 0,-12-8 0,-11-13 0,-7-8 0,-10-9-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3952.48">5766 1349 24575,'2'-9'0,"0"0"0,0 0 0,1 0 0,0 1 0,1-1 0,0 1 0,0 0 0,1 0 0,0 0 0,7-8 0,-6 8 0,128-163 0,10-13 0,-135 170 0,113-162 0,-93 139 0,1 1 0,57-51 0,-35 38 62,22-20-1489,-53 54-5399</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5563.23">5978 412 24575,'11'226'0,"-1"-9"0,-10-152 0,-1-6 0,3 1 0,9 60 0,-7-89 0,-1 0 0,-1 0 0,-2 0 0,-7 55 0,-2-31 0,-29 96 0,33-133-1365,1-4-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 16 24575,'1054'-11'-38,"-700"6"-497,703 39 420,-938-24 125,256 29-31,-269-25 84,158 43 0,-52 6 224,210 90-1,420 153-286,-490-186 0,-171-54 0,165 53 0,-266-94-35,-55-15-187,0-2 0,0 0 1,1-3-1,0 1 1,35 2-1,-38-7-6604</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2558.85">6119 806 24575,'9'3'0,"12"12"0,24 11 0,16 10 0,16 13 0,12 9 0,1 4 0,1 3 0,-7-6 0,-1-1 0,-8-5 0,-13-9 0,-12-12 0,-8-7 0,-11-10-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3952.48">6257 1313 24575,'2'-9'0,"0"0"0,0 1 0,1-1 0,1 1 0,0-1 0,0 2 0,1-1 0,0 0 0,1 0 0,7-7 0,-7 7 0,140-159 0,10-12 0,-146 166 0,122-159 0,-101 136 0,2 1 0,61-49 0,-37 36 62,23-19-1489,-57 52-5399</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5563.2299">6487 401 24575,'12'220'0,"-1"-9"0,-11-148 0,-2-5 0,5 0 0,9 59 0,-8-87 0,-1 0 0,-1 1 0,-2-1 0,-7 53 0,-3-29 0,-31 93 0,35-130-1365,2-3-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1731,18 +1731,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7790D04-D896-42BE-BB0B-3D7C0A5E4DAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:BA26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="18" max="18" width="5.44140625" customWidth="1"/>
-    <col min="35" max="36" width="4.21875" customWidth="1"/>
-    <col min="38" max="43" width="4.6640625" customWidth="1"/>
-    <col min="44" max="44" width="4.21875" customWidth="1"/>
-    <col min="50" max="51" width="2.33203125" customWidth="1"/>
+    <col min="18" max="18" width="5.3984375" customWidth="1"/>
+    <col min="35" max="36" width="4.19921875" customWidth="1"/>
+    <col min="38" max="43" width="4.69921875" customWidth="1"/>
+    <col min="44" max="44" width="4.19921875" customWidth="1"/>
+    <col min="50" max="51" width="2.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:53">
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:53">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:53">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:53">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:53">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:53">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0.12222222222222222</v>
       </c>
     </row>
-    <row r="8" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:53">
       <c r="B8" t="s">
         <v>9</v>
       </c>
@@ -2026,11 +2026,11 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="BA8">
-        <f t="shared" ref="BA7:BA22" si="5">AZ8/2</f>
+        <f t="shared" ref="BA8:BA22" si="5">AZ8/2</f>
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:53">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:53">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:53">
       <c r="B11" t="s">
         <v>6</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:53">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:53">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:53">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:53">
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:53">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:53">
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:53">
       <c r="B18" t="s">
         <v>18</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:53">
       <c r="C19">
         <f>SUM(C2:C18)</f>
         <v>45</v>
@@ -2801,7 +2801,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:53">
       <c r="R20" t="s">
         <v>16</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:53">
       <c r="R21" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:53">
       <c r="R22" t="s">
         <v>18</v>
       </c>
@@ -2978,13 +2978,13 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:53">
       <c r="Z23">
         <f>SUM(Z6:Z22)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:53">
       <c r="S25">
         <f>SUM(S6:S22)</f>
         <v>44</v>
@@ -2997,7 +2997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:53" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:53">
       <c r="AD26">
         <f>8/AD25</f>
         <v>1.8749999999999996</v>
@@ -3008,4 +3008,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Teoría de la información/Árboles.xlsx
+++ b/Teoría de la información/Árboles.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ran\Programas\GitHub\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3885B15D-0D51-42EF-B4AD-6E55380BDA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Huffman" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="64">
   <si>
     <t>12,11</t>
   </si>
@@ -201,13 +191,43 @@
   </si>
   <si>
     <t>11111</t>
+  </si>
+  <si>
+    <t>Una corona di spine</t>
+  </si>
+  <si>
+    <t>Sará il dress-code per la mia festa</t>
+  </si>
+  <si>
+    <t>Contamos cuántas veces aparece cada letra</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Letra</t>
+  </si>
+  <si>
+    <t>Frec Abs</t>
+  </si>
+  <si>
+    <t>Frec Rel</t>
+  </si>
+  <si>
+    <t>12, 11</t>
+  </si>
+  <si>
+    <t>6, 6     ,  6 , 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +237,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -407,10 +441,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -441,9 +476,17 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -464,13 +507,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>350520</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>449580</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -478,7 +521,7 @@
         <xdr:cNvPr id="2" name="Rectángulo 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{139439FC-DED7-FF91-A0A7-39673CE90EB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139439FC-DED7-FF91-A0A7-39673CE90EB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -557,7 +600,7 @@
         <xdr:cNvPr id="3" name="Rectángulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{721A367F-8E73-A319-3916-CCAEC078BE47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{721A367F-8E73-A319-3916-CCAEC078BE47}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -627,7 +670,7 @@
             <xdr14:cNvPr id="4" name="Entrada de lápiz 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7FCF3ACF-104B-A762-72A3-8AA44EB22FC1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FCF3ACF-104B-A762-72A3-8AA44EB22FC1}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -692,7 +735,7 @@
             <xdr14:cNvPr id="7" name="Entrada de lápiz 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E0B0F75-51B2-2D44-6472-0D1D420ABEBC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0B0F75-51B2-2D44-6472-0D1D420ABEBC}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -748,7 +791,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>295080</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>55081</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
       <mc:Choice Requires="xdr14">
@@ -757,7 +800,7 @@
             <xdr14:cNvPr id="8" name="Entrada de lápiz 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C1B94A17-3A72-21BA-901D-37ED9716B0D1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B94A17-3A72-21BA-901D-37ED9716B0D1}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -822,7 +865,7 @@
             <xdr14:cNvPr id="11" name="Entrada de lápiz 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F35F2452-1F9A-59B8-465B-D6D4E4DC01D9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F35F2452-1F9A-59B8-465B-D6D4E4DC01D9}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -887,7 +930,7 @@
             <xdr14:cNvPr id="18" name="Entrada de lápiz 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D78BB5CE-C72C-8865-36B5-2F798DBB6F3D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D78BB5CE-C72C-8865-36B5-2F798DBB6F3D}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -952,7 +995,7 @@
             <xdr14:cNvPr id="25" name="Entrada de lápiz 24">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FFC60CE2-B5CA-2DAD-CED7-437877C0A9FA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC60CE2-B5CA-2DAD-CED7-437877C0A9FA}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1017,7 +1060,7 @@
             <xdr14:cNvPr id="28" name="Entrada de lápiz 27">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5B55704-EE9E-F9E3-C5B6-C6CF5A771209}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B55704-EE9E-F9E3-C5B6-C6CF5A771209}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1080,7 +1123,7 @@
         <xdr:cNvPr id="29" name="Rectángulo 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B5A1BEF7-DADC-490C-404E-546D8F6C5C2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5A1BEF7-DADC-490C-404E-546D8F6C5C2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1148,7 +1191,7 @@
         <xdr:cNvPr id="30" name="Rectángulo 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6616C2D6-5BAA-C4AC-C4A9-4524E177B7E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6616C2D6-5BAA-C4AC-C4A9-4524E177B7E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1240,7 +1283,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">3070 0 24575,'-16'15'0,"0"1"0,-18 25 0,5-6 0,-242 290 0,21 18 0,48-13 0,-242 342 0,308-509 0,-214 196 0,-195 197 0,113-111 0,410-422-83,-148 153 297,138-141-588,3 2 0,2 1 0,-23 43 0,36-54-6452</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2890 0 24575,'-15'16'0,"0"1"0,-17 26 0,5-7 0,-228 305 0,19 19 0,46-13 0,-228 358 0,290-534 0,-201 206 0,-184 206 0,106-116 0,386-443-83,-139 161 297,130-148-588,3 2 0,1 1 0,-21 45 0,34-57-6452</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1267,7 +1310,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"2"0"0,0 0 0,-2 0 0,2 1 0,-1-1 0,-1 2 0,7 1 0,8 3 0,197 70 0,219 110 0,-266-102 0,-5 7 0,209 149 0,262 260 0,-474-363 0,-9 7 0,144 175 0,199 244 0,-256-297 0,-212-236 0,-4-7 0,19 31 0,135 171 0,29 44 0,-163-202 0,73 83 0,-86-118 0,0 0 0,2-3 0,2 0 0,43 28 0,-35-27-1365,-28-18-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"1"0"0,0 0 0,-1 0 0,1 1 0,0-1 0,-1 2 0,6 2 0,7 2 0,181 74 0,201 115 0,-245-107 0,-3 8 0,191 156 0,240 273 0,-435-381 0,-8 7 0,133 184 0,181 256 0,-233-312 0,-196-248 0,-3-7 0,18 33 0,123 179 0,27 47 0,-150-213 0,67 88 0,-78-125 0,-1 1 0,2-4 0,2 1 0,40 29 0,-33-29-1365,-25-18-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1294,7 +1337,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'6'1'0,"1"0"0,-2-1 0,2 2 0,-1-1 0,12 4 0,5 1 0,225 61 0,-212-55 0,1 2 0,-2 0 0,-1 2 0,52 32 0,-70-35 0,0 1 0,0 0 0,-2 0 0,-1 2 0,16 19 0,-2 13 0,-25-42 0,1 1 0,0 0 0,1-1 0,0 0 0,1 1 0,-1-2 0,1 1 0,-1 0 0,2-1 0,8 6 0,362 210 0,-354-208 0,31 18 0,0 4 0,75 65 0,-113-87 0,-1 1 0,16 24 0,-9-14 0,6 22-164,-20-32-1037,0-2-5625</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'5'1'0,"1"0"0,-1-1 0,1 2 0,-1-1 0,11 4 0,4 2 0,198 63 0,-186-57 0,0 1 0,-1 1 0,-1 2 0,46 33 0,-62-36 0,0 0 0,0 1 0,-2 0 0,0 1 0,13 21 0,-1 13 0,-22-43 0,0 0 0,1 0 0,0 0 0,1-1 0,0 1 0,0-1 0,0 0 0,0 0 0,1-1 0,7 7 0,319 220 0,-312-219 0,28 20 0,-1 3 0,67 69 0,-100-91 0,-1 0 0,15 26 0,-9-15 0,6 24-164,-18-35-1037,0-1-5625</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1321,8 +1364,8 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1683 0 24575,'-5'2'0,"1"-1"0,-2 0 0,2 1 0,-1 0 0,0 0 0,0 0 0,1 0 0,0 1 0,-6 5 0,-5 0 0,-49 33 0,3 1 0,0 4 0,-68 69 0,117-106 0,-26 25 0,2 1 0,2 1 0,-53 72 0,-100 205 0,161-273 0,5-6 0,-1-1 0,-36 40 0,8-14 0,2 2 0,-55 94 0,-55 140 0,66-126 0,75-140 0,-1-1 0,-1-1 0,-35 38 0,1-1 0,-103 132-1365,144-183-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1910.02">1616 121 24575,'0'-4'0,"0"0"0,0-1 0,1 1 0,-1-1 0,1 1 0,0 0 0,0-1 0,5-7 0,-6 12 0,1 0 0,-1-1 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,1-1 0,0 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,1 1 0,-2-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,2 2 0,11 6 0,-1 3 0,-1-2 0,0 3 0,-1-2 0,0 2 0,13 19 0,-10-13 0,26 37 0,-3 3 0,-3-1 0,30 74 0,-41-81 0,-9-23 0,-1 0 0,-1 1 0,-3 1 0,-1-1 0,9 54 0,-17-72 0,1-2 0,1 1 0,-1 0 0,2 0 0,0-1 0,0 0 0,9 12 0,45 60 0,-20-31 0,29 37 0,21 31 0,471 877-570,-460-817-700,-93-165-5081</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1583 0 24575,'-5'2'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,0 0 0,1 1 0,0-1 0,0 1 0,-5 5 0,-5 1 0,-47 34 0,4 1 0,0 4 0,-65 72 0,111-110 0,-25 25 0,3 2 0,1 1 0,-50 75 0,-94 215 0,151-286 0,6-6 0,-2-2 0,-33 43 0,6-15 0,3 2 0,-52 98 0,-51 147 0,61-132 0,71-146 0,-1-2 0,0-1 0,-34 41 0,1-2 0,-97 138-1365,136-191-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1910.02">1520 127 24575,'0'-4'0,"0"-1"0,0 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,-1 0 0,6-7 0,-6 12 0,1 0 0,-1-1 0,1-1 0,-1 1 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,0-1 0,1 1 0,0 0 0,1-1 0,0 1 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 1 0,1-1 0,1 1 0,-2-1 0,1 1 0,0-1 0,-1 1 0,1 0 0,1 2 0,12 7 0,-2 2 0,-1-1 0,0 3 0,-1-3 0,1 3 0,11 19 0,-9-13 0,25 39 0,-3 3 0,-3-1 0,28 77 0,-39-85 0,-8-23 0,0-1 0,-2 1 0,-3 2 0,0-2 0,8 57 0,-16-75 0,0-3 0,2 2 0,-1-1 0,2 1 0,0-2 0,-1 1 0,10 12 0,41 62 0,-18-31 0,27 38 0,20 33 0,442 919-570,-432-857-700,-87-172-5081</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1349,10 +1392,10 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1960 141 24575,'-5'1'0,"0"1"0,-1 0 0,0 0 0,1 0 0,0 0 0,-1 0 0,1 1 0,1 0 0,-1 0 0,0 1 0,1-1 0,0 0 0,-8 10 0,2-4 0,-305 283 0,138-121 0,45-47 0,103-95-1365,19-19-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2406.82">2049 0 24575,'13'9'0,"-2"-1"0,2-1 0,1 0 0,-2 0 0,2-1 0,22 6 0,-13-3 0,161 52 0,-148-47 0,-1 1 0,-1 2 0,-2 2 0,51 35 0,-35-22 0,-36-25 0,-1 0 0,1 0 0,-1 2 0,-2-1 0,1 1 0,-1 0 0,11 13 0,-2-1 0,0-2 0,1 1 0,2-2 0,0-1 0,0-1 0,28 15 0,-12-8 0,-27-18 0,0 0 0,-2 1 0,2-1 0,-2 2 0,1 0 0,-1-1 0,0 1 0,10 14 0,58 70 0,-16-21 0,97 124 0,-115-139-1365,-29-41-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6450.08">1043 927 24575,'-1'7'0,"-1"-1"0,0 0 0,-1 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,-1-1 0,-5 5 0,-2 5 0,-43 55 0,-124 120 0,78-88 0,60-58 0,1 3 0,-62 101 0,-23 24 0,60-88 0,11-14 0,-3-3 0,-96 92 0,124-133-1365,20-17-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8599.32">998 887 24575,'1'4'0,"0"0"0,0 0 0,0-1 0,0 0 0,0 0 0,1 1 0,-1-1 0,1 1 0,0-1 0,0-1 0,4 4 0,30 32 0,-35-37 0,53 47 0,3-2 0,120 75 0,-136-97 0,126 85 0,-140-88 0,0 0 0,-2 2 0,41 44 0,-31-27 0,-20-24 0,-2-1 0,20 27 0,-10 8 0,-19-36 0,2-2 0,11 21 0,182 250 0,-44-71 0,128 228 0,-270-419-120,-6-5-58,1-1 0,2 0 0,-1-1 1,2 0-1,1-1 0,20 20 0,-22-25-6648</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1855 148 24575,'-4'1'0,"-1"1"0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 0 0,2 1 0,0 0 0,-1 0 0,0 1 0,2 0 0,-1-1 0,-7 10 0,1-3 0,-288 296 0,130-126 0,43-50 0,98-99-1365,17-21-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2406.82">1940 0 24575,'12'9'0,"-2"0"0,3-2 0,0 1 0,-2-1 0,3-1 0,20 7 0,-13-4 0,154 55 0,-141-49 0,-1 1 0,-1 2 0,-2 2 0,49 36 0,-34-22 0,-33-27 0,-2 1 0,1-1 0,0 2 0,-3 0 0,2 0 0,-2 1 0,11 13 0,-2-1 0,0-2 0,1 1 0,2-2 0,0-1 0,0-2 0,26 17 0,-11-9 0,-25-19 0,-1 1 0,-1 0 0,1-1 0,-1 2 0,0 1 0,0-2 0,0 1 0,9 15 0,55 74 0,-16-22 0,93 129 0,-109-145-1365,-28-43-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6450.08">987 973 24575,'-1'8'0,"0"-2"0,-1 0 0,-1 1 0,0-1 0,0-1 0,-1 2 0,1-1 0,0-1 0,-6 6 0,-1 4 0,-41 59 0,-118 125 0,75-92 0,56-60 0,1 2 0,-59 106 0,-21 26 0,56-93 0,11-14 0,-3-4 0,-91 97 0,118-140-1365,18-17-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8599.32">945 931 24575,'1'5'0,"0"-1"0,0 0 0,0-1 0,0 0 0,-1 0 0,2 2 0,-1-2 0,1 1 0,0-1 0,0-1 0,4 5 0,28 32 0,-33-37 0,50 48 0,3-2 0,113 79 0,-128-102 0,119 90 0,-132-93 0,-1 0 0,-1 2 0,38 47 0,-28-29 0,-20-26 0,-2 0 0,19 28 0,-9 9 0,-18-39 0,2-1 0,10 22 0,172 262 0,-41-75 0,121 240 0,-256-439-120,-5-7-58,0 0 0,3 0 0,-2-1 1,3-1-1,0 0 0,19 21 0,-20-27-6648</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1380,10 +1423,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 16 24575,'1054'-11'-38,"-700"6"-497,703 39 420,-938-24 125,256 29-31,-269-25 84,158 43 0,-52 6 224,210 90-1,420 153-286,-490-186 0,-171-54 0,165 53 0,-266-94-35,-55-15-187,0-2 0,0 0 1,1-3-1,0 1 1,35 2-1,-38-7-6604</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2558.85">6119 806 24575,'9'3'0,"12"12"0,24 11 0,16 10 0,16 13 0,12 9 0,1 4 0,1 3 0,-7-6 0,-1-1 0,-8-5 0,-13-9 0,-12-12 0,-8-7 0,-11-10-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3952.48">6257 1313 24575,'2'-9'0,"0"0"0,0 1 0,1-1 0,1 1 0,0-1 0,0 2 0,1-1 0,0 0 0,1 0 0,7-7 0,-7 7 0,140-159 0,10-12 0,-146 166 0,122-159 0,-101 136 0,2 1 0,61-49 0,-37 36 62,23-19-1489,-57 52-5399</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5563.2299">6487 401 24575,'12'220'0,"-1"-9"0,-11-148 0,-2-5 0,5 0 0,9 59 0,-8-87 0,-1 0 0,-1 1 0,-2-1 0,-7 53 0,-3-29 0,-31 93 0,35-130-1365,2-3-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 17 24575,'974'-12'-38,"-647"7"-497,649 40 420,-866-24 125,236 30-31,-248-27 84,146 46 0,-48 6 224,194 93-1,387 161-286,-452-195 0,-157-56 0,151 55 0,-245-98-35,-51-15-187,0-3 0,0 1 1,1-4-1,0 1 1,33 2-1,-36-7-6604</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2558.85">5652 842 24575,'8'3'0,"12"12"0,21 12 0,16 11 0,14 13 0,11 10 0,1 4 0,1 2 0,-6-5 0,-2-1 0,-6-6 0,-13-9 0,-11-13 0,-7-7 0,-10-10-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3952.48">5780 1371 24575,'1'-10'0,"1"1"0,0 1 0,1-2 0,1 2 0,-1-1 0,1 1 0,1 0 0,-1 0 0,2-1 0,6-6 0,-7 6 0,130-165 0,9-13 0,-135 173 0,113-165 0,-93 141 0,1 2 0,57-52 0,-34 38 62,21-20-1489,-53 54-5399</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5563.22">5992 419 24575,'11'229'0,"-1"-8"0,-10-156 0,-2-4 0,5 0 0,8 61 0,-7-91 0,-1 0 0,-1 2 0,-2-2 0,-7 56 0,-2-31 0,-29 98 0,32-137-1365,3-2-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1731,50 +1774,320 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:BA26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:M24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="18" max="18" width="5.3984375" customWidth="1"/>
-    <col min="35" max="36" width="4.19921875" customWidth="1"/>
-    <col min="38" max="43" width="4.69921875" customWidth="1"/>
-    <col min="44" max="44" width="4.19921875" customWidth="1"/>
-    <col min="50" max="51" width="2.296875" customWidth="1"/>
+    <col min="12" max="12" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:53">
-      <c r="B2" t="s">
+    <row r="2" spans="2:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="2:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34">
+        <v>45</v>
+      </c>
+      <c r="M3" s="34"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K4" s="34">
+        <v>23</v>
+      </c>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C7">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="2:53">
-      <c r="B3" t="s">
+      <c r="D7" s="33">
+        <f>C7 / $C$24</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" s="33">
+        <f>C8 / $C$24</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C9">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:53">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
+      <c r="D9" s="33">
+        <f>C9 / $C$24</f>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" s="33">
+        <f>C10 / $C$24</f>
+        <v>8.8888888888888892E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="33">
+        <f>C11 / $C$24</f>
+        <v>8.8888888888888892E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="33">
+        <f>C12 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="33">
+        <f>C13 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" s="33">
+        <f>C14 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="33">
+        <f>C15 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="33">
+        <f>C16 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" s="33">
+        <f>C17 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="33">
+        <f>C18 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="33">
+        <f>C19 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="33">
+        <f>C20 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33">
+        <f>C21 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="33">
+        <f>C22 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33">
+        <f>C23 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <f>SUM(C7:C23)</f>
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:BA65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="5.88671875" customWidth="1"/>
+    <col min="18" max="18" width="5.44140625" customWidth="1"/>
+    <col min="35" max="36" width="4.21875" customWidth="1"/>
+    <col min="38" max="43" width="4.6640625" customWidth="1"/>
+    <col min="44" max="44" width="4.21875" customWidth="1"/>
+    <col min="50" max="51" width="2.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:53" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:53" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:53" x14ac:dyDescent="0.3">
       <c r="AE4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:53">
+    <row r="5" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="AI5" t="s">
         <v>3</v>
@@ -1795,18 +2108,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:53">
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
+    <row r="6" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B6" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
       </c>
       <c r="R6" t="s">
         <v>3</v>
@@ -1878,18 +2188,16 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:53">
+    <row r="7" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D7" s="33">
+        <f>C7 / $C$24</f>
+        <v>0.13333333333333333</v>
       </c>
       <c r="R7" t="s">
         <v>4</v>
@@ -1959,15 +2267,16 @@
         <v>0.12222222222222222</v>
       </c>
     </row>
-    <row r="8" spans="2:53">
+    <row r="8" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D8" s="33">
+        <f>C8 / $C$24</f>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R8" t="s">
         <v>5</v>
@@ -2030,12 +2339,16 @@
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:53">
+    <row r="9" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="33">
+        <f>C9 / $C$24</f>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R9" t="s">
         <v>6</v>
@@ -2102,12 +2415,16 @@
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:53">
+    <row r="10" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D10" s="33">
+        <f>C10 / $C$24</f>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="R10" t="s">
         <v>7</v>
@@ -2170,12 +2487,16 @@
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:53">
+    <row r="11" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D11" s="33">
+        <f>C11 / $C$24</f>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="R11" t="s">
         <v>8</v>
@@ -2240,12 +2561,16 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:53">
+    <row r="12" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D12" s="33">
+        <f>C12 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="R12" t="s">
         <v>9</v>
@@ -2308,12 +2633,16 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:53">
+    <row r="13" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D13" s="33">
+        <f>C13 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -2380,12 +2709,16 @@
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:53">
+    <row r="14" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D14" s="33">
+        <f>C14 / $C$24</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="R14" t="s">
         <v>11</v>
@@ -2448,12 +2781,16 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:53">
+    <row r="15" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="33">
+        <f>C15 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="R15" t="s">
         <v>6</v>
@@ -2517,12 +2854,16 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:53">
+    <row r="16" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="33">
+        <f>C16 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="R16" t="s">
         <v>12</v>
@@ -2590,12 +2931,16 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:53">
+    <row r="17" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="33">
+        <f>C17 / $C$24</f>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="R17" t="s">
         <v>13</v>
@@ -2660,12 +3005,16 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:53">
+    <row r="18" spans="2:53" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>1</v>
+      </c>
+      <c r="D18" s="33">
+        <f>C18 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="R18" t="s">
         <v>14</v>
@@ -2732,10 +3081,16 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:53">
+    <row r="19" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
       <c r="C19">
-        <f>SUM(C2:C18)</f>
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="D19" s="33">
+        <f>C19 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="R19" t="s">
         <v>15</v>
@@ -2801,7 +3156,17 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:53">
+    <row r="20" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="33">
+        <f>C20 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
       <c r="R20" t="s">
         <v>16</v>
       </c>
@@ -2864,7 +3229,17 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:53">
+    <row r="21" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33">
+        <f>C21 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
       <c r="R21" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +3310,17 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:53">
+    <row r="22" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="33">
+        <f>C22 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
       <c r="R22" t="s">
         <v>18</v>
       </c>
@@ -2978,13 +3363,29 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:53">
+    <row r="23" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33">
+        <f>C23 / $C$24</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
       <c r="Z23">
         <f>SUM(Z6:Z22)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="2:53">
+    <row r="24" spans="2:53" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <f>SUM(C7:C23)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="2:53" x14ac:dyDescent="0.3">
       <c r="S25">
         <f>SUM(S6:S22)</f>
         <v>44</v>
@@ -2997,24 +3398,176 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:53">
+    <row r="26" spans="2:53" x14ac:dyDescent="0.3">
       <c r="AD26">
         <f>8/AD25</f>
         <v>1.8749999999999996</v>
       </c>
     </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <v>23</v>
+      </c>
+      <c r="H52">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="G53" t="s">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65">
+        <f>SUM(C48:C64)</f>
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B22">
+    <sortCondition ref="B6:B22"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Teoría de la información/Árboles.xlsx
+++ b/Teoría de la información/Árboles.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3885B15D-0D51-42EF-B4AD-6E55380BDA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6452F4CB-54FF-4A4A-8CC3-1698714091FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Huffman" sheetId="2" r:id="rId1"/>
+    <sheet name="Shannon" sheetId="2" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="65">
   <si>
     <t>12,11</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>6, 6     ,  6 , 5</t>
+  </si>
+  <si>
+    <t>Frec Acum</t>
   </si>
 </sst>
 </file>
@@ -225,7 +228,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -445,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -479,10 +482,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1830,6 +1834,9 @@
       <c r="D6" t="s">
         <v>61</v>
       </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
       <c r="K6" s="34" t="s">
         <v>63</v>
       </c>
@@ -1844,8 +1851,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="33">
-        <f>C7 / $C$24</f>
+        <f t="shared" ref="D7:D23" si="0">C7 / $C$24</f>
         <v>0.13333333333333333</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
       </c>
       <c r="K7" s="34"/>
       <c r="L7" s="34"/>
@@ -1859,8 +1869,12 @@
         <v>5</v>
       </c>
       <c r="D8" s="33">
-        <f>C8 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
+      </c>
+      <c r="E8" s="35">
+        <f>D7 + E7</f>
+        <v>0.13333333333333333</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -1874,8 +1888,12 @@
         <v>5</v>
       </c>
       <c r="D9" s="33">
-        <f>C9 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
+      </c>
+      <c r="E9" s="35">
+        <f t="shared" ref="E9:E23" si="1">D8 + E8</f>
+        <v>0.24444444444444444</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
@@ -1886,8 +1904,12 @@
         <v>4</v>
       </c>
       <c r="D10" s="33">
-        <f>C10 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="E10" s="35">
+        <f t="shared" si="1"/>
+        <v>0.35555555555555551</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
@@ -1898,8 +1920,12 @@
         <v>4</v>
       </c>
       <c r="D11" s="33">
-        <f>C11 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="E11" s="35">
+        <f t="shared" si="1"/>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
@@ -1910,8 +1936,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="33">
-        <f>C12 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E12" s="35">
+        <f t="shared" si="1"/>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.3">
@@ -1922,8 +1952,12 @@
         <v>3</v>
       </c>
       <c r="D13" s="33">
-        <f>C13 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E13" s="35">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
@@ -1934,8 +1968,12 @@
         <v>3</v>
       </c>
       <c r="D14" s="33">
-        <f>C14 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E14" s="35">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.3">
@@ -1946,8 +1984,12 @@
         <v>2</v>
       </c>
       <c r="D15" s="33">
-        <f>C15 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="E15" s="35">
+        <f t="shared" si="1"/>
+        <v>0.73333333333333328</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
@@ -1958,11 +2000,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="33">
-        <f>C16 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="35">
+        <f t="shared" si="1"/>
+        <v>0.77777777777777768</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>40</v>
       </c>
@@ -1970,11 +2016,15 @@
         <v>2</v>
       </c>
       <c r="D17" s="33">
-        <f>C17 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="35">
+        <f t="shared" si="1"/>
+        <v>0.82222222222222208</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -1982,11 +2032,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="33">
-        <f>C18 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="35">
+        <f t="shared" si="1"/>
+        <v>0.86666666666666647</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>18</v>
       </c>
@@ -1994,11 +2048,15 @@
         <v>1</v>
       </c>
       <c r="D19" s="33">
-        <f>C19 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="35">
+        <f t="shared" si="1"/>
+        <v>0.88888888888888873</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>58</v>
       </c>
@@ -2006,11 +2064,15 @@
         <v>1</v>
       </c>
       <c r="D20" s="33">
-        <f>C20 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="35">
+        <f t="shared" si="1"/>
+        <v>0.91111111111111098</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>14</v>
       </c>
@@ -2018,11 +2080,15 @@
         <v>1</v>
       </c>
       <c r="D21" s="33">
-        <f>C21 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="35">
+        <f t="shared" si="1"/>
+        <v>0.93333333333333324</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>13</v>
       </c>
@@ -2030,11 +2096,15 @@
         <v>1</v>
       </c>
       <c r="D22" s="33">
-        <f>C22 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="35">
+        <f t="shared" si="1"/>
+        <v>0.95555555555555549</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>15</v>
       </c>
@@ -2042,11 +2112,15 @@
         <v>1</v>
       </c>
       <c r="D23" s="33">
-        <f>C23 / $C$24</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="35">
+        <f t="shared" si="1"/>
+        <v>0.97777777777777775</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C24">
         <f>SUM(C7:C23)</f>
         <v>45</v>
@@ -2054,6 +2128,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2196,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="33">
-        <f>C7 / $C$24</f>
+        <f t="shared" ref="D7:D23" si="1">C7 / $C$24</f>
         <v>0.13333333333333333</v>
       </c>
       <c r="R7" t="s">
@@ -2218,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <f t="shared" ref="AA7:AA22" si="1">Z7 / $Z$23</f>
+        <f t="shared" ref="AA7:AA22" si="2">Z7 / $Z$23</f>
         <v>0.1111111111111111</v>
       </c>
       <c r="AB7">
@@ -2226,7 +2301,7 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="AC7">
-        <f t="shared" ref="AC7:AC22" si="2">ROUNDUP(LOG(1/AA7,2),0)</f>
+        <f t="shared" ref="AC7:AC22" si="3">ROUNDUP(LOG(1/AA7,2),0)</f>
         <v>4</v>
       </c>
       <c r="AD7" s="1" t="s">
@@ -2259,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="AZ7">
-        <f t="shared" ref="AZ7:AZ22" si="3">AY7 / $Z$23</f>
+        <f t="shared" ref="AZ7:AZ22" si="4">AY7 / $Z$23</f>
         <v>0.1111111111111111</v>
       </c>
       <c r="BA7">
@@ -2275,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="33">
-        <f>C8 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="R8" t="s">
@@ -2291,15 +2366,15 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="AB8">
-        <f t="shared" ref="AB8:AB22" si="4">AA7 + AB7</f>
+        <f t="shared" ref="AB8:AB22" si="5">AA7 + AB7</f>
         <v>0.24444444444444444</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD8" s="1" t="s">
@@ -2331,11 +2406,11 @@
         <v>5</v>
       </c>
       <c r="AZ8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="BA8">
-        <f t="shared" ref="BA8:BA22" si="5">AZ8/2</f>
+        <f t="shared" ref="BA8:BA22" si="6">AZ8/2</f>
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
@@ -2347,7 +2422,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="33">
-        <f>C9 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="R9" t="s">
@@ -2363,15 +2438,15 @@
         <v>4</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.35555555555555551</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD9" s="1" t="s">
@@ -2407,11 +2482,11 @@
         <v>4</v>
       </c>
       <c r="AZ9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="BA9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
@@ -2423,7 +2498,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="33">
-        <f>C10 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="R10" t="s">
@@ -2439,15 +2514,15 @@
         <v>4</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD10" s="1" t="s">
@@ -2479,11 +2554,11 @@
         <v>4</v>
       </c>
       <c r="AZ10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="BA10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
@@ -2495,7 +2570,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="33">
-        <f>C11 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="R11" t="s">
@@ -2511,15 +2586,15 @@
         <v>3</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.53333333333333333</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD11" s="1" t="s">
@@ -2553,11 +2628,11 @@
         <v>3</v>
       </c>
       <c r="AZ11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="BA11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
@@ -2569,7 +2644,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="33">
-        <f>C12 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="R12" t="s">
@@ -2585,15 +2660,15 @@
         <v>3</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD12" s="1" t="s">
@@ -2625,11 +2700,11 @@
         <v>3</v>
       </c>
       <c r="AZ12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="BA12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
@@ -2641,7 +2716,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="33">
-        <f>C13 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="R13" t="s">
@@ -2657,15 +2732,15 @@
         <v>3</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AD13" s="1" t="s">
@@ -2701,11 +2776,11 @@
         <v>3</v>
       </c>
       <c r="AZ13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="BA13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
@@ -2717,7 +2792,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="33">
-        <f>C14 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="R14" t="s">
@@ -2733,15 +2808,15 @@
         <v>2</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.73333333333333328</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="AD14" s="1" t="s">
@@ -2773,11 +2848,11 @@
         <v>2</v>
       </c>
       <c r="AZ14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="BA14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
@@ -2789,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="33">
-        <f>C15 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="R15" t="s">
@@ -2805,15 +2880,15 @@
         <v>2</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.77777777777777768</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="AD15" s="1" t="s">
@@ -2846,11 +2921,11 @@
         <v>2</v>
       </c>
       <c r="AZ15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="BA15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
@@ -2862,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="33">
-        <f>C16 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="R16" t="s">
@@ -2878,15 +2953,15 @@
         <v>2</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.82222222222222208</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="AD16" s="1" t="s">
@@ -2923,11 +2998,11 @@
         <v>2</v>
       </c>
       <c r="AZ16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="BA16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
@@ -2939,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="33">
-        <f>C17 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="R17" t="s">
@@ -2955,15 +3030,15 @@
         <v>1</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.86666666666666647</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD17" s="1" t="s">
@@ -2997,11 +3072,11 @@
         <v>1</v>
       </c>
       <c r="AZ17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3013,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="33">
-        <f>C18 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="R18" t="s">
@@ -3029,15 +3104,15 @@
         <v>1</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.88888888888888873</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD18" s="1" t="s">
@@ -3073,11 +3148,11 @@
         <v>1</v>
       </c>
       <c r="AZ18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3089,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="33">
-        <f>C19 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="R19" t="s">
@@ -3105,15 +3180,15 @@
         <v>1</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.91111111111111098</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD19" s="1" t="s">
@@ -3148,11 +3223,11 @@
         <v>1</v>
       </c>
       <c r="AZ19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3164,7 +3239,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="33">
-        <f>C20 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="R20" t="s">
@@ -3180,15 +3255,15 @@
         <v>1</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.93333333333333324</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD20" s="1" t="s">
@@ -3221,11 +3296,11 @@
         <v>1</v>
       </c>
       <c r="AZ20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3237,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="33">
-        <f>C21 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="R21" t="s">
@@ -3253,15 +3328,15 @@
         <v>1</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.95555555555555549</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD21" s="1" t="s">
@@ -3302,11 +3377,11 @@
         <v>1</v>
       </c>
       <c r="AZ21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3318,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="33">
-        <f>C22 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="R22" t="s">
@@ -3334,15 +3409,15 @@
         <v>1</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.97777777777777775</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AD22" s="1" t="s">
@@ -3355,11 +3430,11 @@
         <v>1</v>
       </c>
       <c r="AZ22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="BA22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
@@ -3371,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="33">
-        <f>C23 / $C$24</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="Z23">
